--- a/data/HISTORIA_Donostia_San_Sebastian_Klasikoa.xlsx
+++ b/data/HISTORIA_Donostia_San_Sebastian_Klasikoa.xlsx
@@ -960,7 +960,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>one_day_races:808,gc:607</t>
+          <t>one_day_races:902,climber:618</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>one_day_races:1640,climber:1106</t>
+          <t>one_day_races:1677,climber:1118</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>INEOS Grenadiers</t>
+          <t>Movistar Team</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Movistar Team</t>
+          <t>Bahrain - Victorious</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bahrain - Victorious</t>
+          <t>INEOS Grenadiers</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>one_day_races:5392,hills:2502</t>
+          <t>one_day_races:5397,hills:2504</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>EF Education - EasyPost</t>
+          <t>Israel - Premier Tech</t>
         </is>
       </c>
       <c r="H78" t="n">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Israel - Premier Tech</t>
+          <t>EF Education - EasyPost</t>
         </is>
       </c>
       <c r="H79" t="n">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>one_day_races:808,gc:607</t>
+          <t>one_day_races:902,climber:618</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bahrain - Victorious</t>
+          <t>Groupama - FDJ</t>
         </is>
       </c>
       <c r="H84" t="n">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Groupama - FDJ</t>
+          <t>Uno-X Mobility</t>
         </is>
       </c>
       <c r="H85" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Uno-X Mobility</t>
+          <t>Bahrain - Victorious</t>
         </is>
       </c>
       <c r="H86" t="n">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Movistar Team</t>
+          <t>Astana Qazaqstan Team</t>
         </is>
       </c>
       <c r="H88" t="n">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Team Visma | Lease a Bike</t>
+          <t>Movistar Team</t>
         </is>
       </c>
       <c r="H90" t="n">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Astana Qazaqstan Team</t>
+          <t>Team Visma | Lease a Bike</t>
         </is>
       </c>
       <c r="H91" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alpecin - Deceuninck</t>
+          <t>Euskaltel - Euskadi</t>
         </is>
       </c>
       <c r="H94" t="n">
@@ -2733,7 +2733,7 @@
     <row r="95">
       <c r="G95" t="inlineStr">
         <is>
-          <t>Euskaltel - Euskadi</t>
+          <t>Alpecin - Deceuninck</t>
         </is>
       </c>
       <c r="H95" t="n">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>hills:2687,one_day_races:2679</t>
+          <t>one_day_races:2709,hills:2696</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>one_day_races:1599,hills:1250</t>
+          <t>one_day_races:1626,hills:1256</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>INEOS Grenadiers</t>
+          <t>Israel - Premier Tech</t>
         </is>
       </c>
       <c r="H129" t="n">
@@ -3529,7 +3529,7 @@
     <row r="130">
       <c r="G130" t="inlineStr">
         <is>
-          <t>Israel - Premier Tech</t>
+          <t>INEOS Grenadiers</t>
         </is>
       </c>
       <c r="H130" t="n">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>gc:2385,climber:2316</t>
+          <t>gc:2385,climber:2340</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>BORA - hansgrohe</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="H178" t="n">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>TotalEnergies</t>
+          <t>BORA - hansgrohe</t>
         </is>
       </c>
       <c r="H179" t="n">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>one_day_races:3090,hills:2926</t>
+          <t>one_day_races:3090,hills:2927</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -5498,7 +5498,7 @@
     <row r="225">
       <c r="G225" t="inlineStr">
         <is>
-          <t>Caja Rural - Seguros RGA</t>
+          <t>Team Arkéa Samsic</t>
         </is>
       </c>
       <c r="H225" t="n">
@@ -5508,7 +5508,7 @@
     <row r="226">
       <c r="G226" t="inlineStr">
         <is>
-          <t>Team Arkéa Samsic</t>
+          <t>Caja Rural - Seguros RGA</t>
         </is>
       </c>
       <c r="H226" t="n">
@@ -5954,7 +5954,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sergio Geovani Chumil</t>
+          <t>Josh Burnett</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -5977,7 +5977,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Josh Burnett</t>
+          <t>Sergio Geovani Chumil</t>
         </is>
       </c>
       <c r="B14" t="n">
